--- a/Nigeria_crop.xlsx
+++ b/Nigeria_crop.xlsx
@@ -1,25 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10911"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10817"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ubcca-my.sharepoint.com/personal/hisham_zerriffi_ubc_ca/Documents/Admin/Grad Students/Abdulateef Gafar/Adbulateef Gafar PhD Files/Chaps/GEPOnSSET/Bio-scripts/git-version/gep-bioenergy/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ubcca-my.sharepoint.com/personal/hisham_zerriffi_ubc_ca/Documents/Admin/Grad Students/Abdulateef Gafar/Adbulateef Gafar PhD Files/Chaps/GEPOnSSET/GEP_Bioenergy/gep_bio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="31" documentId="13_ncr:1_{B1307807-6F8E-BB4A-AAB1-8CA8D85D103B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2CD8E55A-392D-9C42-A2AB-48B6EB57E58E}"/>
+  <xr:revisionPtr revIDLastSave="34" documentId="13_ncr:1_{B1307807-6F8E-BB4A-AAB1-8CA8D85D103B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FF13E6CB-8465-D64A-8ECC-2C80BD658763}"/>
   <bookViews>
-    <workbookView xWindow="180" yWindow="820" windowWidth="13320" windowHeight="17660" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="180" yWindow="820" windowWidth="24140" windowHeight="17660" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="state" sheetId="1" r:id="rId1"/>
-    <sheet name="state1" sheetId="5" r:id="rId2"/>
-    <sheet name="crop" sheetId="2" r:id="rId3"/>
-    <sheet name="bounds" sheetId="3" r:id="rId4"/>
+    <sheet name="crop" sheetId="2" r:id="rId2"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId5"/>
+    <externalReference r:id="rId3"/>
   </externalReferences>
   <definedNames>
     <definedName name="million">'[1]Gasifier sys'!$F$52</definedName>
@@ -60,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="45">
   <si>
     <t>Abia</t>
   </si>
@@ -195,12 +193,6 @@
   </si>
   <si>
     <t>rice</t>
-  </si>
-  <si>
-    <t>PercentageArea</t>
-  </si>
-  <si>
-    <t>ResidueEnergyYield (Mj/ha)</t>
   </si>
 </sst>
 </file>
@@ -756,6 +748,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Sheet1"/>
@@ -798,9 +791,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -838,7 +831,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -944,7 +937,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1086,7 +1079,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1117,9 +1110,7 @@
       <c r="B1" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="C1" s="3" t="s">
-        <v>45</v>
-      </c>
+      <c r="C1" s="3"/>
       <c r="D1" s="3"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
@@ -1129,9 +1120,6 @@
       <c r="B2" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="C2">
-        <v>0.5</v>
-      </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
@@ -1140,9 +1128,6 @@
       <c r="B3" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C3">
-        <v>0.5</v>
-      </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
@@ -1151,9 +1136,6 @@
       <c r="B4" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="C4">
-        <v>0.5</v>
-      </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
@@ -1162,9 +1144,6 @@
       <c r="B5" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="C5">
-        <v>0.5</v>
-      </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
@@ -1173,9 +1152,6 @@
       <c r="B6" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="C6">
-        <v>0.5</v>
-      </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
@@ -1184,9 +1160,6 @@
       <c r="B7" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C7">
-        <v>0.5</v>
-      </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
@@ -1195,9 +1168,6 @@
       <c r="B8" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="C8">
-        <v>0.5</v>
-      </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
@@ -1206,9 +1176,6 @@
       <c r="B9" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="C9">
-        <v>0.5</v>
-      </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
@@ -1217,9 +1184,6 @@
       <c r="B10" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C10">
-        <v>0.5</v>
-      </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
@@ -1228,9 +1192,6 @@
       <c r="B11" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="C11">
-        <v>0.5</v>
-      </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
@@ -1239,9 +1200,6 @@
       <c r="B12" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="C12">
-        <v>0.5</v>
-      </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
@@ -1250,9 +1208,6 @@
       <c r="B13" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="C13">
-        <v>0.5</v>
-      </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
@@ -1261,9 +1216,6 @@
       <c r="B14" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="C14">
-        <v>0.5</v>
-      </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
@@ -1272,9 +1224,6 @@
       <c r="B15" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="C15">
-        <v>0.5</v>
-      </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
@@ -1283,250 +1232,181 @@
       <c r="B16" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="C16">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
         <v>15</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C17">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
         <v>16</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="C18">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
         <v>17</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="C19">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
         <v>18</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="C20">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
         <v>19</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="C21">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
         <v>20</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C22">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
         <v>21</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="C23">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
         <v>22</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="C24">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
         <v>23</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="C25">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A26" s="2" t="s">
         <v>24</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="C26">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A27" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="C27">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A28" s="2" t="s">
         <v>25</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="C28">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A29" s="2" t="s">
         <v>26</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="C29">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A30" s="2" t="s">
         <v>27</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="C30">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A31" s="2" t="s">
         <v>28</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="C31">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A32" s="2" t="s">
         <v>29</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="C32">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A33" s="2" t="s">
         <v>30</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C33">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A34" s="2" t="s">
         <v>31</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="C34">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A35" s="2" t="s">
         <v>32</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="C35">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A36" s="2" t="s">
         <v>33</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="C36">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.2">
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A37" s="2" t="s">
         <v>34</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="C37">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.2">
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A38" s="2" t="s">
         <v>35</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>39</v>
-      </c>
-      <c r="C38">
-        <v>0.5</v>
       </c>
     </row>
   </sheetData>
@@ -1535,440 +1415,6 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{908F8E95-6E8C-DD45-9211-9F3A2229B4CC}">
-  <dimension ref="A1:D38"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="14.6640625" style="2" customWidth="1"/>
-    <col min="2" max="2" width="10.83203125" style="2"/>
-    <col min="3" max="3" width="14.1640625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="D1" s="3"/>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A2" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="C2">
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A3" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="C3">
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A4" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="C4">
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A5" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="C5">
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A6" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="C6">
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A7" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="C7">
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A8" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="C8">
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A9" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="C9">
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A10" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="C10">
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A11" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="C11">
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A12" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="C12">
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A13" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="C13">
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A14" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="C14">
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A15" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="C15">
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A16" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="C16">
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A17" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="C17">
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A18" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="C18">
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A19" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="C19">
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A20" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="C20">
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A21" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="C21">
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A22" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="C22">
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A23" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="C23">
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A24" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="C24">
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A25" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="C25">
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A26" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="C26">
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A27" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="C27">
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A28" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="C28">
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A29" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="C29">
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A30" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="C30">
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A31" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="C31">
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A32" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="B32" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="C32">
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A33" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="B33" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="C33">
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A34" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B34" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="C34">
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A35" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B35" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="C35">
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A36" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="B36" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="C36">
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A37" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B37" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="C37">
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A38" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B38" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="C38">
-        <v>0.15</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -2036,88 +1482,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F919CAC1-CA60-A746-9E91-C0F6793C49DD}">
-  <dimension ref="A1:E4"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="5" max="5" width="24.5" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A1" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>39</v>
-      </c>
-      <c r="B2">
-        <v>1.4</v>
-      </c>
-      <c r="C2">
-        <v>16.3</v>
-      </c>
-      <c r="D2">
-        <v>2.2326000000000001</v>
-      </c>
-      <c r="E2">
-        <f>B2*C2*D2</f>
-        <v>50.947932000000002</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B3">
-        <v>0.6</v>
-      </c>
-      <c r="C3">
-        <v>16.399999999999999</v>
-      </c>
-      <c r="D3">
-        <v>6.3459000000000003</v>
-      </c>
-      <c r="E3">
-        <f t="shared" ref="E3:E4" si="0">B3*C3*D3</f>
-        <v>62.44365599999999</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>44</v>
-      </c>
-      <c r="B4">
-        <v>2.1800000000000002</v>
-      </c>
-      <c r="C4">
-        <v>12.4</v>
-      </c>
-      <c r="D4">
-        <v>1.974</v>
-      </c>
-      <c r="E4">
-        <f t="shared" si="0"/>
-        <v>53.361168000000006</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>